--- a/Team-Data/2007-08/12-1-2007-08.xlsx
+++ b/Team-Data/2007-08/12-1-2007-08.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,16 +806,16 @@
         <v>-2.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AE2" t="n">
         <v>19</v>
       </c>
       <c r="AF2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AG2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH2" t="n">
         <v>1</v>
@@ -775,7 +842,7 @@
         <v>12</v>
       </c>
       <c r="AP2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ2" t="n">
         <v>13</v>
@@ -787,13 +854,13 @@
         <v>29</v>
       </c>
       <c r="AT2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AU2" t="n">
         <v>26</v>
       </c>
       <c r="AV2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AW2" t="n">
         <v>9</v>
@@ -805,16 +872,16 @@
         <v>27</v>
       </c>
       <c r="AZ2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BB2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>12-1-2007-08</t>
+          <t>2007-12-01</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>13.7</v>
       </c>
       <c r="AD3" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AE3" t="n">
         <v>3</v>
@@ -951,13 +1018,13 @@
         <v>13</v>
       </c>
       <c r="AN3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AO3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AP3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ3" t="n">
         <v>14</v>
@@ -969,13 +1036,13 @@
         <v>5</v>
       </c>
       <c r="AT3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU3" t="n">
         <v>3</v>
       </c>
       <c r="AV3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW3" t="n">
         <v>3</v>
@@ -987,13 +1054,13 @@
         <v>21</v>
       </c>
       <c r="AZ3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA3" t="n">
         <v>9</v>
       </c>
       <c r="BB3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BC3" t="n">
         <v>1</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>12-1-2007-08</t>
+          <t>2007-12-01</t>
         </is>
       </c>
     </row>
@@ -1025,64 +1092,64 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E4" t="n">
         <v>6</v>
       </c>
       <c r="F4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4</v>
+        <v>0.429</v>
       </c>
       <c r="H4" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="I4" t="n">
-        <v>34.8</v>
+        <v>34.6</v>
       </c>
       <c r="J4" t="n">
-        <v>79.2</v>
+        <v>79.5</v>
       </c>
       <c r="K4" t="n">
-        <v>0.439</v>
+        <v>0.436</v>
       </c>
       <c r="L4" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="M4" t="n">
-        <v>16.9</v>
+        <v>16.7</v>
       </c>
       <c r="N4" t="n">
-        <v>0.379</v>
+        <v>0.372</v>
       </c>
       <c r="O4" t="n">
-        <v>17.3</v>
+        <v>17.7</v>
       </c>
       <c r="P4" t="n">
-        <v>25.7</v>
+        <v>25.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.674</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="R4" t="n">
-        <v>12.9</v>
+        <v>13.2</v>
       </c>
       <c r="S4" t="n">
-        <v>28.8</v>
+        <v>29.7</v>
       </c>
       <c r="T4" t="n">
-        <v>41.7</v>
+        <v>42.9</v>
       </c>
       <c r="U4" t="n">
-        <v>19.6</v>
+        <v>19.4</v>
       </c>
       <c r="V4" t="n">
         <v>17.1</v>
       </c>
       <c r="W4" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="X4" t="n">
         <v>4.8</v>
@@ -1091,52 +1158,52 @@
         <v>6.3</v>
       </c>
       <c r="Z4" t="n">
-        <v>23.5</v>
+        <v>23.7</v>
       </c>
       <c r="AA4" t="n">
-        <v>21</v>
+        <v>21.3</v>
       </c>
       <c r="AB4" t="n">
-        <v>93.3</v>
+        <v>93.2</v>
       </c>
       <c r="AC4" t="n">
-        <v>-4.9</v>
+        <v>-4.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AE4" t="n">
         <v>19</v>
       </c>
       <c r="AF4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AG4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AH4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AI4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AJ4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL4" t="n">
         <v>13</v>
       </c>
       <c r="AM4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AN4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AO4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AP4" t="n">
         <v>16</v>
@@ -1148,37 +1215,37 @@
         <v>3</v>
       </c>
       <c r="AS4" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AT4" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="AU4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AV4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AW4" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AX4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AY4" t="n">
         <v>30</v>
       </c>
       <c r="AZ4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BA4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BB4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>12-1-2007-08</t>
+          <t>2007-12-01</t>
         </is>
       </c>
     </row>
@@ -1207,100 +1274,100 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
         <v>10</v>
       </c>
       <c r="G5" t="n">
-        <v>0.286</v>
+        <v>0.231</v>
       </c>
       <c r="H5" t="n">
         <v>48.4</v>
       </c>
       <c r="I5" t="n">
-        <v>34.1</v>
+        <v>33.3</v>
       </c>
       <c r="J5" t="n">
-        <v>85.90000000000001</v>
+        <v>86.2</v>
       </c>
       <c r="K5" t="n">
-        <v>0.397</v>
+        <v>0.386</v>
       </c>
       <c r="L5" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="M5" t="n">
-        <v>16.7</v>
+        <v>17.2</v>
       </c>
       <c r="N5" t="n">
-        <v>0.303</v>
+        <v>0.29</v>
       </c>
       <c r="O5" t="n">
-        <v>15.3</v>
+        <v>15.2</v>
       </c>
       <c r="P5" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.716</v>
+        <v>0.704</v>
       </c>
       <c r="R5" t="n">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="S5" t="n">
-        <v>29.9</v>
+        <v>30</v>
       </c>
       <c r="T5" t="n">
-        <v>44.4</v>
+        <v>44.2</v>
       </c>
       <c r="U5" t="n">
-        <v>20.4</v>
+        <v>20</v>
       </c>
       <c r="V5" t="n">
-        <v>16.4</v>
+        <v>15.8</v>
       </c>
       <c r="W5" t="n">
         <v>8.1</v>
       </c>
       <c r="X5" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Z5" t="n">
-        <v>21.9</v>
+        <v>22.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>88.5</v>
+        <v>86.8</v>
       </c>
       <c r="AC5" t="n">
-        <v>-6.6</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="AD5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AE5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AF5" t="n">
         <v>22</v>
       </c>
       <c r="AG5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AH5" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AI5" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AJ5" t="n">
         <v>4</v>
@@ -1312,7 +1379,7 @@
         <v>23</v>
       </c>
       <c r="AM5" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AN5" t="n">
         <v>30</v>
@@ -1324,22 +1391,22 @@
         <v>26</v>
       </c>
       <c r="AQ5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AR5" t="n">
         <v>1</v>
       </c>
       <c r="AS5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AT5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AU5" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AV5" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="AW5" t="n">
         <v>8</v>
@@ -1351,7 +1418,7 @@
         <v>26</v>
       </c>
       <c r="AZ5" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="BA5" t="n">
         <v>18</v>
@@ -1360,7 +1427,7 @@
         <v>30</v>
       </c>
       <c r="BC5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>12-1-2007-08</t>
+          <t>2007-12-01</t>
         </is>
       </c>
     </row>
@@ -1467,22 +1534,22 @@
         <v>-3.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF6" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI6" t="n">
         <v>12</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>7</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>14</v>
       </c>
       <c r="AJ6" t="n">
         <v>8</v>
@@ -1494,31 +1561,31 @@
         <v>10</v>
       </c>
       <c r="AM6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AN6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AO6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP6" t="n">
         <v>17</v>
       </c>
       <c r="AQ6" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AR6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AS6" t="n">
         <v>12</v>
       </c>
       <c r="AT6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AU6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AV6" t="n">
         <v>13</v>
@@ -1527,22 +1594,22 @@
         <v>17</v>
       </c>
       <c r="AX6" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AY6" t="n">
         <v>20</v>
       </c>
       <c r="AZ6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA6" t="n">
         <v>26</v>
       </c>
       <c r="BB6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>12-1-2007-08</t>
+          <t>2007-12-01</t>
         </is>
       </c>
     </row>
@@ -1571,37 +1638,37 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E7" t="n">
         <v>11</v>
       </c>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G7" t="n">
-        <v>0.647</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>48.3</v>
+        <v>48</v>
       </c>
       <c r="I7" t="n">
-        <v>37</v>
+        <v>36.9</v>
       </c>
       <c r="J7" t="n">
-        <v>80.09999999999999</v>
+        <v>79.5</v>
       </c>
       <c r="K7" t="n">
-        <v>0.462</v>
+        <v>0.464</v>
       </c>
       <c r="L7" t="n">
         <v>5.6</v>
       </c>
       <c r="M7" t="n">
-        <v>17</v>
+        <v>16.8</v>
       </c>
       <c r="N7" t="n">
-        <v>0.329</v>
+        <v>0.331</v>
       </c>
       <c r="O7" t="n">
         <v>22.9</v>
@@ -1610,76 +1677,76 @@
         <v>27.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.839</v>
+        <v>0.834</v>
       </c>
       <c r="R7" t="n">
         <v>10.6</v>
       </c>
       <c r="S7" t="n">
-        <v>31.9</v>
+        <v>31.8</v>
       </c>
       <c r="T7" t="n">
-        <v>42.5</v>
+        <v>42.4</v>
       </c>
       <c r="U7" t="n">
-        <v>20.6</v>
+        <v>20.4</v>
       </c>
       <c r="V7" t="n">
-        <v>12.2</v>
+        <v>12.4</v>
       </c>
       <c r="W7" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="X7" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Y7" t="n">
         <v>4.3</v>
       </c>
       <c r="Z7" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="AA7" t="n">
-        <v>22.2</v>
+        <v>22.4</v>
       </c>
       <c r="AB7" t="n">
-        <v>102.5</v>
+        <v>102.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="AD7" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AE7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AG7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>14</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK7" t="n">
         <v>8</v>
       </c>
-      <c r="AH7" t="n">
-        <v>15</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>13</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>18</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>10</v>
-      </c>
       <c r="AL7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AM7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AN7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO7" t="n">
         <v>4</v>
@@ -1697,22 +1764,22 @@
         <v>11</v>
       </c>
       <c r="AT7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU7" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AV7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW7" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AX7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY7" t="n">
         <v>9</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>8</v>
       </c>
       <c r="AZ7" t="n">
         <v>22</v>
@@ -1721,7 +1788,7 @@
         <v>12</v>
       </c>
       <c r="BB7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BC7" t="n">
         <v>7</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>12-1-2007-08</t>
+          <t>2007-12-01</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>3.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE8" t="n">
         <v>8</v>
@@ -1843,7 +1910,7 @@
         <v>9</v>
       </c>
       <c r="AH8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI8" t="n">
         <v>5</v>
@@ -1861,7 +1928,7 @@
         <v>7</v>
       </c>
       <c r="AN8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO8" t="n">
         <v>5</v>
@@ -1870,7 +1937,7 @@
         <v>1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR8" t="n">
         <v>16</v>
@@ -1882,10 +1949,10 @@
         <v>7</v>
       </c>
       <c r="AU8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV8" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AW8" t="n">
         <v>1</v>
@@ -1897,10 +1964,10 @@
         <v>10</v>
       </c>
       <c r="AZ8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB8" t="n">
         <v>4</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>12-1-2007-08</t>
+          <t>2007-12-01</t>
         </is>
       </c>
     </row>
@@ -1935,61 +2002,61 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F9" t="n">
         <v>5</v>
       </c>
       <c r="G9" t="n">
-        <v>0.667</v>
+        <v>0.643</v>
       </c>
       <c r="H9" t="n">
         <v>48</v>
       </c>
       <c r="I9" t="n">
-        <v>37.8</v>
+        <v>37.4</v>
       </c>
       <c r="J9" t="n">
-        <v>80.3</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>0.471</v>
+        <v>0.467</v>
       </c>
       <c r="L9" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="M9" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="N9" t="n">
-        <v>0.361</v>
+        <v>0.353</v>
       </c>
       <c r="O9" t="n">
-        <v>18.3</v>
+        <v>18.1</v>
       </c>
       <c r="P9" t="n">
-        <v>25.3</v>
+        <v>25.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.724</v>
+        <v>0.713</v>
       </c>
       <c r="R9" t="n">
-        <v>11.9</v>
+        <v>11.6</v>
       </c>
       <c r="S9" t="n">
-        <v>29.2</v>
+        <v>29.7</v>
       </c>
       <c r="T9" t="n">
-        <v>41.1</v>
+        <v>41.4</v>
       </c>
       <c r="U9" t="n">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="V9" t="n">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="W9" t="n">
         <v>7</v>
@@ -1998,97 +2065,97 @@
         <v>5.3</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>20.5</v>
+        <v>20.2</v>
       </c>
       <c r="AA9" t="n">
-        <v>20.6</v>
+        <v>20.4</v>
       </c>
       <c r="AB9" t="n">
-        <v>99.5</v>
+        <v>98.3</v>
       </c>
       <c r="AC9" t="n">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AE9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF9" t="n">
         <v>5</v>
       </c>
       <c r="AG9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>19</v>
+      </c>
+      <c r="AK9" t="n">
         <v>6</v>
       </c>
-      <c r="AH9" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>16</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>5</v>
-      </c>
       <c r="AL9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AM9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>18</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>18</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>23</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>24</v>
+      </c>
+      <c r="AT9" t="n">
         <v>22</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>17</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>19</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>21</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>27</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>21</v>
       </c>
       <c r="AU9" t="n">
         <v>4</v>
       </c>
       <c r="AV9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW9" t="n">
         <v>20</v>
       </c>
       <c r="AX9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AY9" t="n">
         <v>1</v>
       </c>
       <c r="AZ9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA9" t="n">
         <v>24</v>
       </c>
       <c r="BB9" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="BC9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>12-1-2007-08</t>
+          <t>2007-12-01</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>0.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AE10" t="n">
         <v>14</v>
@@ -2204,10 +2271,10 @@
         <v>9</v>
       </c>
       <c r="AG10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH10" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AI10" t="n">
         <v>2</v>
@@ -2225,19 +2292,19 @@
         <v>1</v>
       </c>
       <c r="AN10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO10" t="n">
         <v>16</v>
       </c>
       <c r="AP10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ10" t="n">
         <v>28</v>
       </c>
       <c r="AR10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AS10" t="n">
         <v>23</v>
@@ -2249,7 +2316,7 @@
         <v>11</v>
       </c>
       <c r="AV10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW10" t="n">
         <v>6</v>
@@ -2261,7 +2328,7 @@
         <v>19</v>
       </c>
       <c r="AZ10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BA10" t="n">
         <v>8</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>12-1-2007-08</t>
+          <t>2007-12-01</t>
         </is>
       </c>
     </row>
@@ -2299,64 +2366,64 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E11" t="n">
         <v>9</v>
       </c>
       <c r="F11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5</v>
+        <v>0.529</v>
       </c>
       <c r="H11" t="n">
         <v>48</v>
       </c>
       <c r="I11" t="n">
-        <v>36.3</v>
+        <v>36.4</v>
       </c>
       <c r="J11" t="n">
         <v>82.59999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>0.44</v>
+        <v>0.441</v>
       </c>
       <c r="L11" t="n">
         <v>6.1</v>
       </c>
       <c r="M11" t="n">
-        <v>19.7</v>
+        <v>19.4</v>
       </c>
       <c r="N11" t="n">
-        <v>0.311</v>
+        <v>0.312</v>
       </c>
       <c r="O11" t="n">
-        <v>16.7</v>
+        <v>16.4</v>
       </c>
       <c r="P11" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.732</v>
+        <v>0.723</v>
       </c>
       <c r="R11" t="n">
         <v>12.6</v>
       </c>
       <c r="S11" t="n">
-        <v>32.1</v>
+        <v>31.9</v>
       </c>
       <c r="T11" t="n">
-        <v>44.7</v>
+        <v>44.5</v>
       </c>
       <c r="U11" t="n">
-        <v>20.6</v>
+        <v>20.9</v>
       </c>
       <c r="V11" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="W11" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="X11" t="n">
         <v>4.8</v>
@@ -2365,49 +2432,49 @@
         <v>4.6</v>
       </c>
       <c r="Z11" t="n">
-        <v>21.7</v>
+        <v>21.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>20.6</v>
+        <v>20.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>95.5</v>
+        <v>95.3</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="AD11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF11" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AG11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI11" t="n">
         <v>19</v>
       </c>
       <c r="AJ11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AK11" t="n">
         <v>22</v>
       </c>
       <c r="AL11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AN11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AO11" t="n">
         <v>23</v>
@@ -2416,40 +2483,40 @@
         <v>23</v>
       </c>
       <c r="AQ11" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AR11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AS11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AT11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AU11" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AV11" t="n">
         <v>7</v>
       </c>
       <c r="AW11" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AX11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ11" t="n">
         <v>12</v>
       </c>
       <c r="BA11" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BB11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BC11" t="n">
         <v>12</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>12-1-2007-08</t>
+          <t>2007-12-01</t>
         </is>
       </c>
     </row>
@@ -2559,13 +2626,13 @@
         <v>-1.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE12" t="n">
         <v>14</v>
       </c>
       <c r="AF12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AG12" t="n">
         <v>16</v>
@@ -2574,7 +2641,7 @@
         <v>15</v>
       </c>
       <c r="AI12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AJ12" t="n">
         <v>3</v>
@@ -2598,10 +2665,10 @@
         <v>14</v>
       </c>
       <c r="AQ12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AS12" t="n">
         <v>3</v>
@@ -2613,28 +2680,28 @@
         <v>9</v>
       </c>
       <c r="AV12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AW12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY12" t="n">
         <v>25</v>
       </c>
       <c r="AZ12" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BA12" t="n">
         <v>10</v>
       </c>
       <c r="BB12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BC12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>12-1-2007-08</t>
+          <t>2007-12-01</t>
         </is>
       </c>
     </row>
@@ -2741,22 +2808,22 @@
         <v>-5.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AE13" t="n">
         <v>19</v>
       </c>
       <c r="AF13" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AG13" t="n">
         <v>19</v>
       </c>
       <c r="AH13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI13" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AJ13" t="n">
         <v>21</v>
@@ -2765,22 +2832,22 @@
         <v>28</v>
       </c>
       <c r="AL13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AM13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AN13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO13" t="n">
         <v>6</v>
       </c>
       <c r="AP13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AR13" t="n">
         <v>20</v>
@@ -2789,10 +2856,10 @@
         <v>6</v>
       </c>
       <c r="AT13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AV13" t="n">
         <v>17</v>
@@ -2801,7 +2868,7 @@
         <v>26</v>
       </c>
       <c r="AX13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AY13" t="n">
         <v>22</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>12-1-2007-08</t>
+          <t>2007-12-01</t>
         </is>
       </c>
     </row>
@@ -2923,10 +2990,10 @@
         <v>4.1</v>
       </c>
       <c r="AD14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AE14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF14" t="n">
         <v>9</v>
@@ -2935,16 +3002,16 @@
         <v>10</v>
       </c>
       <c r="AH14" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AJ14" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AK14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AL14" t="n">
         <v>12</v>
@@ -2953,7 +3020,7 @@
         <v>12</v>
       </c>
       <c r="AN14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO14" t="n">
         <v>2</v>
@@ -2962,7 +3029,7 @@
         <v>2</v>
       </c>
       <c r="AQ14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AR14" t="n">
         <v>16</v>
@@ -2971,7 +3038,7 @@
         <v>4</v>
       </c>
       <c r="AT14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AU14" t="n">
         <v>8</v>
@@ -2986,19 +3053,19 @@
         <v>22</v>
       </c>
       <c r="AY14" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AZ14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB14" t="n">
         <v>5</v>
       </c>
       <c r="BC14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>12-1-2007-08</t>
+          <t>2007-12-01</t>
         </is>
       </c>
     </row>
@@ -3027,88 +3094,88 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F15" t="n">
         <v>10</v>
       </c>
       <c r="G15" t="n">
-        <v>0.375</v>
+        <v>0.333</v>
       </c>
       <c r="H15" t="n">
         <v>48.3</v>
       </c>
       <c r="I15" t="n">
-        <v>37.4</v>
+        <v>37.1</v>
       </c>
       <c r="J15" t="n">
-        <v>80.40000000000001</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>0.466</v>
+        <v>0.464</v>
       </c>
       <c r="L15" t="n">
-        <v>8.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>21.4</v>
+        <v>20.9</v>
       </c>
       <c r="N15" t="n">
-        <v>0.401</v>
+        <v>0.396</v>
       </c>
       <c r="O15" t="n">
-        <v>21.1</v>
+        <v>21.7</v>
       </c>
       <c r="P15" t="n">
-        <v>27.6</v>
+        <v>28.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.762</v>
+        <v>0.765</v>
       </c>
       <c r="R15" t="n">
         <v>9.6</v>
       </c>
       <c r="S15" t="n">
-        <v>32.4</v>
+        <v>31.9</v>
       </c>
       <c r="T15" t="n">
-        <v>42.1</v>
+        <v>41.5</v>
       </c>
       <c r="U15" t="n">
-        <v>21.5</v>
+        <v>21</v>
       </c>
       <c r="V15" t="n">
         <v>15.6</v>
       </c>
       <c r="W15" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="X15" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Z15" t="n">
-        <v>19.8</v>
+        <v>20</v>
       </c>
       <c r="AA15" t="n">
-        <v>23.6</v>
+        <v>24</v>
       </c>
       <c r="AB15" t="n">
-        <v>104.5</v>
+        <v>104.2</v>
       </c>
       <c r="AC15" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="AD15" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AE15" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AF15" t="n">
         <v>22</v>
@@ -3117,70 +3184,70 @@
         <v>22</v>
       </c>
       <c r="AH15" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AI15" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AJ15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK15" t="n">
         <v>9</v>
       </c>
       <c r="AL15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AM15" t="n">
         <v>5</v>
       </c>
       <c r="AN15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO15" t="n">
+        <v>7</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>7</v>
+      </c>
+      <c r="AQ15" t="n">
         <v>9</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>9</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>10</v>
       </c>
       <c r="AR15" t="n">
         <v>24</v>
       </c>
       <c r="AS15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AT15" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AU15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AV15" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>30</v>
+      </c>
+      <c r="AX15" t="n">
         <v>15</v>
       </c>
-      <c r="AW15" t="n">
-        <v>29</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>7</v>
-      </c>
       <c r="AY15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BA15" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BB15" t="n">
         <v>6</v>
       </c>
       <c r="BC15" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>12-1-2007-08</t>
+          <t>2007-12-01</t>
         </is>
       </c>
     </row>
@@ -3287,40 +3354,40 @@
         <v>-3.7</v>
       </c>
       <c r="AD16" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AE16" t="n">
         <v>27</v>
       </c>
       <c r="AF16" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG16" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AH16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI16" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AJ16" t="n">
         <v>29</v>
       </c>
       <c r="AK16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AM16" t="n">
         <v>24</v>
       </c>
       <c r="AN16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO16" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP16" t="n">
         <v>21</v>
@@ -3332,7 +3399,7 @@
         <v>30</v>
       </c>
       <c r="AS16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT16" t="n">
         <v>30</v>
@@ -3341,28 +3408,28 @@
         <v>27</v>
       </c>
       <c r="AV16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW16" t="n">
         <v>7</v>
       </c>
       <c r="AX16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AY16" t="n">
         <v>3</v>
       </c>
       <c r="AZ16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB16" t="n">
         <v>29</v>
       </c>
       <c r="BC16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>12-1-2007-08</t>
+          <t>2007-12-01</t>
         </is>
       </c>
     </row>
@@ -3391,106 +3458,106 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E17" t="n">
         <v>7</v>
       </c>
       <c r="F17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G17" t="n">
-        <v>0.467</v>
+        <v>0.5</v>
       </c>
       <c r="H17" t="n">
         <v>48</v>
       </c>
       <c r="I17" t="n">
-        <v>36.8</v>
+        <v>36.6</v>
       </c>
       <c r="J17" t="n">
-        <v>79</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>0.466</v>
+        <v>0.46</v>
       </c>
       <c r="L17" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="M17" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="N17" t="n">
-        <v>0.324</v>
+        <v>0.325</v>
       </c>
       <c r="O17" t="n">
-        <v>17.1</v>
+        <v>17.6</v>
       </c>
       <c r="P17" t="n">
-        <v>23.4</v>
+        <v>23.6</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.729</v>
+        <v>0.748</v>
       </c>
       <c r="R17" t="n">
-        <v>11.5</v>
+        <v>11.9</v>
       </c>
       <c r="S17" t="n">
-        <v>29.3</v>
+        <v>29.6</v>
       </c>
       <c r="T17" t="n">
-        <v>40.8</v>
+        <v>41.6</v>
       </c>
       <c r="U17" t="n">
-        <v>21</v>
+        <v>20.7</v>
       </c>
       <c r="V17" t="n">
-        <v>15</v>
+        <v>14.7</v>
       </c>
       <c r="W17" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="X17" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Y17" t="n">
         <v>5.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="AA17" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="AB17" t="n">
-        <v>95.40000000000001</v>
+        <v>95.7</v>
       </c>
       <c r="AC17" t="n">
-        <v>-4.3</v>
+        <v>-2.8</v>
       </c>
       <c r="AD17" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>17</v>
+      </c>
+      <c r="AJ17" t="n">
         <v>20</v>
       </c>
-      <c r="AE17" t="n">
-        <v>18</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>18</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>15</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>23</v>
-      </c>
       <c r="AK17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AL17" t="n">
         <v>27</v>
@@ -3502,25 +3569,25 @@
         <v>24</v>
       </c>
       <c r="AO17" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AP17" t="n">
         <v>22</v>
       </c>
       <c r="AQ17" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AR17" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AS17" t="n">
         <v>26</v>
       </c>
       <c r="AT17" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AU17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AV17" t="n">
         <v>10</v>
@@ -3529,22 +3596,22 @@
         <v>25</v>
       </c>
       <c r="AX17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AZ17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB17" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BC17" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>12-1-2007-08</t>
+          <t>2007-12-01</t>
         </is>
       </c>
     </row>
@@ -3573,85 +3640,85 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E18" t="n">
         <v>2</v>
       </c>
       <c r="F18" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G18" t="n">
-        <v>0.133</v>
+        <v>0.143</v>
       </c>
       <c r="H18" t="n">
         <v>48</v>
       </c>
       <c r="I18" t="n">
-        <v>36.4</v>
+        <v>36.6</v>
       </c>
       <c r="J18" t="n">
-        <v>81.7</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>0.445</v>
+        <v>0.45</v>
       </c>
       <c r="L18" t="n">
         <v>6</v>
       </c>
       <c r="M18" t="n">
-        <v>16.5</v>
+        <v>16.1</v>
       </c>
       <c r="N18" t="n">
-        <v>0.363</v>
+        <v>0.372</v>
       </c>
       <c r="O18" t="n">
-        <v>14.2</v>
+        <v>14.6</v>
       </c>
       <c r="P18" t="n">
-        <v>19.8</v>
+        <v>20.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.717</v>
+        <v>0.719</v>
       </c>
       <c r="R18" t="n">
-        <v>12.1</v>
+        <v>12.3</v>
       </c>
       <c r="S18" t="n">
-        <v>28.5</v>
+        <v>28.1</v>
       </c>
       <c r="T18" t="n">
-        <v>40.6</v>
+        <v>40.4</v>
       </c>
       <c r="U18" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="V18" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="W18" t="n">
         <v>7.7</v>
       </c>
       <c r="X18" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Y18" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="Z18" t="n">
-        <v>25.3</v>
+        <v>25.9</v>
       </c>
       <c r="AA18" t="n">
-        <v>18.6</v>
+        <v>18.8</v>
       </c>
       <c r="AB18" t="n">
-        <v>93</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="AC18" t="n">
-        <v>-9</v>
+        <v>-7.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3663,34 +3730,34 @@
         <v>30</v>
       </c>
       <c r="AH18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AJ18" t="n">
         <v>12</v>
       </c>
       <c r="AK18" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AL18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AM18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AN18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO18" t="n">
         <v>30</v>
       </c>
       <c r="AP18" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AQ18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AR18" t="n">
         <v>11</v>
@@ -3699,13 +3766,13 @@
         <v>30</v>
       </c>
       <c r="AT18" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AU18" t="n">
         <v>28</v>
       </c>
       <c r="AV18" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AW18" t="n">
         <v>12</v>
@@ -3714,19 +3781,19 @@
         <v>19</v>
       </c>
       <c r="AY18" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AZ18" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BA18" t="n">
         <v>29</v>
       </c>
       <c r="BB18" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="BC18" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>12-1-2007-08</t>
+          <t>2007-12-01</t>
         </is>
       </c>
     </row>
@@ -3755,97 +3822,97 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F19" t="n">
         <v>8</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5</v>
+        <v>0.467</v>
       </c>
       <c r="H19" t="n">
-        <v>48.6</v>
+        <v>48.3</v>
       </c>
       <c r="I19" t="n">
         <v>31.1</v>
       </c>
       <c r="J19" t="n">
-        <v>74.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="K19" t="n">
-        <v>0.415</v>
+        <v>0.416</v>
       </c>
       <c r="L19" t="n">
         <v>5.6</v>
       </c>
       <c r="M19" t="n">
-        <v>18.2</v>
+        <v>17.8</v>
       </c>
       <c r="N19" t="n">
-        <v>0.309</v>
+        <v>0.315</v>
       </c>
       <c r="O19" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="P19" t="n">
         <v>29.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.739</v>
+        <v>0.734</v>
       </c>
       <c r="R19" t="n">
         <v>9.9</v>
       </c>
       <c r="S19" t="n">
-        <v>30.4</v>
+        <v>30.7</v>
       </c>
       <c r="T19" t="n">
-        <v>40.3</v>
+        <v>40.6</v>
       </c>
       <c r="U19" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="V19" t="n">
-        <v>17.3</v>
+        <v>17.5</v>
       </c>
       <c r="W19" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="X19" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Y19" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="Z19" t="n">
         <v>24.6</v>
       </c>
       <c r="AA19" t="n">
-        <v>24.8</v>
+        <v>24.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>89.7</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="AC19" t="n">
-        <v>-6.3</v>
+        <v>-6.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AE19" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF19" t="n">
         <v>14</v>
       </c>
-      <c r="AF19" t="n">
-        <v>12</v>
-      </c>
       <c r="AG19" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AH19" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AI19" t="n">
         <v>30</v>
@@ -3860,10 +3927,10 @@
         <v>18</v>
       </c>
       <c r="AM19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AN19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AO19" t="n">
         <v>7</v>
@@ -3872,16 +3939,16 @@
         <v>5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AR19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS19" t="n">
         <v>18</v>
       </c>
       <c r="AT19" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AU19" t="n">
         <v>10</v>
@@ -3896,13 +3963,13 @@
         <v>12</v>
       </c>
       <c r="AY19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ19" t="n">
         <v>28</v>
       </c>
       <c r="BA19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB19" t="n">
         <v>28</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>12-1-2007-08</t>
+          <t>2007-12-01</t>
         </is>
       </c>
     </row>
@@ -3937,64 +4004,64 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F20" t="n">
         <v>6</v>
       </c>
       <c r="G20" t="n">
-        <v>0.667</v>
+        <v>0.647</v>
       </c>
       <c r="H20" t="n">
-        <v>48.6</v>
+        <v>48.3</v>
       </c>
       <c r="I20" t="n">
-        <v>36.3</v>
+        <v>36.2</v>
       </c>
       <c r="J20" t="n">
-        <v>81.8</v>
+        <v>81.5</v>
       </c>
       <c r="K20" t="n">
         <v>0.444</v>
       </c>
       <c r="L20" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="M20" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.388</v>
+      </c>
+      <c r="O20" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="P20" t="n">
         <v>20</v>
       </c>
-      <c r="N20" t="n">
-        <v>0.386</v>
-      </c>
-      <c r="O20" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="P20" t="n">
-        <v>20.8</v>
-      </c>
       <c r="Q20" t="n">
-        <v>0.797</v>
+        <v>0.788</v>
       </c>
       <c r="R20" t="n">
-        <v>10.8</v>
+        <v>10.6</v>
       </c>
       <c r="S20" t="n">
         <v>31.3</v>
       </c>
       <c r="T20" t="n">
-        <v>42.2</v>
+        <v>41.9</v>
       </c>
       <c r="U20" t="n">
         <v>20.2</v>
       </c>
       <c r="V20" t="n">
-        <v>13.2</v>
+        <v>13.5</v>
       </c>
       <c r="W20" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="X20" t="n">
         <v>3.8</v>
@@ -4006,28 +4073,28 @@
         <v>19.7</v>
       </c>
       <c r="AA20" t="n">
-        <v>19.7</v>
+        <v>19.4</v>
       </c>
       <c r="AB20" t="n">
-        <v>96.8</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="AC20" t="n">
         <v>3.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AF20" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG20" t="n">
         <v>7</v>
       </c>
-      <c r="AG20" t="n">
-        <v>6</v>
-      </c>
       <c r="AH20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AI20" t="n">
         <v>20</v>
@@ -4042,37 +4109,37 @@
         <v>7</v>
       </c>
       <c r="AM20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AN20" t="n">
         <v>5</v>
       </c>
       <c r="AO20" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AP20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AR20" t="n">
         <v>18</v>
       </c>
       <c r="AS20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AT20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AV20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW20" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AX20" t="n">
         <v>28</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>12-1-2007-08</t>
+          <t>2007-12-01</t>
         </is>
       </c>
     </row>
@@ -4197,16 +4264,16 @@
         <v>-8.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AE21" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AF21" t="n">
         <v>22</v>
       </c>
       <c r="AG21" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AH21" t="n">
         <v>1</v>
@@ -4236,10 +4303,10 @@
         <v>15</v>
       </c>
       <c r="AQ21" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AR21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AS21" t="n">
         <v>17</v>
@@ -4269,10 +4336,10 @@
         <v>11</v>
       </c>
       <c r="BB21" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BC21" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>12-1-2007-08</t>
+          <t>2007-12-01</t>
         </is>
       </c>
     </row>
@@ -4391,13 +4458,13 @@
         <v>3</v>
       </c>
       <c r="AH22" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI22" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AJ22" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK22" t="n">
         <v>7</v>
@@ -4412,13 +4479,13 @@
         <v>15</v>
       </c>
       <c r="AO22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP22" t="n">
         <v>6</v>
       </c>
       <c r="AQ22" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AR22" t="n">
         <v>28</v>
@@ -4427,16 +4494,16 @@
         <v>1</v>
       </c>
       <c r="AT22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AU22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AV22" t="n">
         <v>8</v>
       </c>
       <c r="AW22" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AX22" t="n">
         <v>23</v>
@@ -4445,7 +4512,7 @@
         <v>5</v>
       </c>
       <c r="AZ22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA22" t="n">
         <v>5</v>
@@ -4454,7 +4521,7 @@
         <v>7</v>
       </c>
       <c r="BC22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BD22" t="n">
         <v>10</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>12-1-2007-08</t>
+          <t>2007-12-01</t>
         </is>
       </c>
     </row>
@@ -4483,109 +4550,109 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E23" t="n">
         <v>5</v>
       </c>
       <c r="F23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G23" t="n">
-        <v>0.313</v>
+        <v>0.333</v>
       </c>
       <c r="H23" t="n">
-        <v>48.6</v>
+        <v>48.3</v>
       </c>
       <c r="I23" t="n">
-        <v>34.6</v>
+        <v>34.9</v>
       </c>
       <c r="J23" t="n">
-        <v>79.59999999999999</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>0.435</v>
+        <v>0.436</v>
       </c>
       <c r="L23" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="M23" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="N23" t="n">
-        <v>0.308</v>
+        <v>0.311</v>
       </c>
       <c r="O23" t="n">
-        <v>18</v>
+        <v>17.4</v>
       </c>
       <c r="P23" t="n">
-        <v>25.5</v>
+        <v>25</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.706</v>
+        <v>0.696</v>
       </c>
       <c r="R23" t="n">
-        <v>13.5</v>
+        <v>13.7</v>
       </c>
       <c r="S23" t="n">
-        <v>30</v>
+        <v>29.8</v>
       </c>
       <c r="T23" t="n">
         <v>43.5</v>
       </c>
       <c r="U23" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="V23" t="n">
-        <v>16.3</v>
+        <v>16.2</v>
       </c>
       <c r="W23" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="X23" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Y23" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="Z23" t="n">
-        <v>21.7</v>
+        <v>21.3</v>
       </c>
       <c r="AA23" t="n">
-        <v>20.7</v>
+        <v>20.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>91.59999999999999</v>
+        <v>91.5</v>
       </c>
       <c r="AC23" t="n">
         <v>-2.8</v>
       </c>
       <c r="AD23" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AE23" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AF23" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AG23" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AH23" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AI23" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AJ23" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AK23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL23" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AM23" t="n">
         <v>27</v>
@@ -4594,43 +4661,43 @@
         <v>29</v>
       </c>
       <c r="AO23" t="n">
+        <v>21</v>
+      </c>
+      <c r="AP23" t="n">
         <v>19</v>
       </c>
-      <c r="AP23" t="n">
-        <v>18</v>
-      </c>
       <c r="AQ23" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AR23" t="n">
         <v>2</v>
       </c>
       <c r="AS23" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AT23" t="n">
         <v>10</v>
       </c>
       <c r="AU23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AV23" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW23" t="n">
         <v>19</v>
       </c>
       <c r="AX23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AY23" t="n">
         <v>13</v>
       </c>
       <c r="AZ23" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BA23" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB23" t="n">
         <v>26</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>12-1-2007-08</t>
+          <t>2007-12-01</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>5.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AE24" t="n">
         <v>4</v>
@@ -4755,7 +4822,7 @@
         <v>4</v>
       </c>
       <c r="AH24" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI24" t="n">
         <v>1</v>
@@ -4773,10 +4840,10 @@
         <v>3</v>
       </c>
       <c r="AN24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO24" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AP24" t="n">
         <v>24</v>
@@ -4791,7 +4858,7 @@
         <v>2</v>
       </c>
       <c r="AT24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU24" t="n">
         <v>2</v>
@@ -4806,7 +4873,7 @@
         <v>3</v>
       </c>
       <c r="AY24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AZ24" t="n">
         <v>2</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>12-1-2007-08</t>
+          <t>2007-12-01</t>
         </is>
       </c>
     </row>
@@ -4925,19 +4992,19 @@
         <v>-5.3</v>
       </c>
       <c r="AD25" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AE25" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AF25" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG25" t="n">
         <v>26</v>
       </c>
-      <c r="AG25" t="n">
-        <v>25</v>
-      </c>
       <c r="AH25" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI25" t="n">
         <v>22</v>
@@ -4949,37 +5016,37 @@
         <v>13</v>
       </c>
       <c r="AL25" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AM25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AN25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO25" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AP25" t="n">
         <v>25</v>
       </c>
       <c r="AQ25" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AR25" t="n">
         <v>25</v>
       </c>
       <c r="AS25" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AT25" t="n">
         <v>29</v>
       </c>
       <c r="AU25" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AV25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW25" t="n">
         <v>27</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>12-1-2007-08</t>
+          <t>2007-12-01</t>
         </is>
       </c>
     </row>
@@ -5029,43 +5096,43 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F26" t="n">
         <v>10</v>
       </c>
       <c r="G26" t="n">
-        <v>0.375</v>
+        <v>0.333</v>
       </c>
       <c r="H26" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="I26" t="n">
-        <v>35.3</v>
+        <v>35.1</v>
       </c>
       <c r="J26" t="n">
-        <v>78.90000000000001</v>
+        <v>78.3</v>
       </c>
       <c r="K26" t="n">
         <v>0.448</v>
       </c>
       <c r="L26" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="M26" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="N26" t="n">
-        <v>0.336</v>
+        <v>0.339</v>
       </c>
       <c r="O26" t="n">
         <v>24.1</v>
       </c>
       <c r="P26" t="n">
-        <v>29.8</v>
+        <v>29.7</v>
       </c>
       <c r="Q26" t="n">
         <v>0.8090000000000001</v>
@@ -5074,43 +5141,43 @@
         <v>9.9</v>
       </c>
       <c r="S26" t="n">
-        <v>29.6</v>
+        <v>29.5</v>
       </c>
       <c r="T26" t="n">
-        <v>39.6</v>
+        <v>39.4</v>
       </c>
       <c r="U26" t="n">
         <v>16.1</v>
       </c>
       <c r="V26" t="n">
-        <v>15.4</v>
+        <v>16.1</v>
       </c>
       <c r="W26" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="X26" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Y26" t="n">
         <v>5.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>22.1</v>
+        <v>22.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>25.4</v>
+        <v>25.3</v>
       </c>
       <c r="AB26" t="n">
-        <v>99.90000000000001</v>
+        <v>99.5</v>
       </c>
       <c r="AC26" t="n">
-        <v>-3.8</v>
+        <v>-4.6</v>
       </c>
       <c r="AD26" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AE26" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AF26" t="n">
         <v>22</v>
@@ -5119,16 +5186,16 @@
         <v>22</v>
       </c>
       <c r="AH26" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AI26" t="n">
         <v>21</v>
       </c>
       <c r="AJ26" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL26" t="n">
         <v>22</v>
@@ -5137,7 +5204,7 @@
         <v>23</v>
       </c>
       <c r="AN26" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AO26" t="n">
         <v>1</v>
@@ -5149,10 +5216,10 @@
         <v>3</v>
       </c>
       <c r="AR26" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS26" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AT26" t="n">
         <v>28</v>
@@ -5161,7 +5228,7 @@
         <v>30</v>
       </c>
       <c r="AV26" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AW26" t="n">
         <v>18</v>
@@ -5170,10 +5237,10 @@
         <v>29</v>
       </c>
       <c r="AY26" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ26" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BA26" t="n">
         <v>1</v>
@@ -5182,7 +5249,7 @@
         <v>13</v>
       </c>
       <c r="BC26" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>12-1-2007-08</t>
+          <t>2007-12-01</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE27" t="n">
         <v>1</v>
@@ -5301,19 +5368,19 @@
         <v>2</v>
       </c>
       <c r="AH27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI27" t="n">
         <v>4</v>
       </c>
       <c r="AJ27" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AK27" t="n">
         <v>3</v>
       </c>
       <c r="AL27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AM27" t="n">
         <v>6</v>
@@ -5322,7 +5389,7 @@
         <v>2</v>
       </c>
       <c r="AO27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP27" t="n">
         <v>27</v>
@@ -5334,7 +5401,7 @@
         <v>26</v>
       </c>
       <c r="AS27" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AT27" t="n">
         <v>26</v>
@@ -5349,7 +5416,7 @@
         <v>22</v>
       </c>
       <c r="AX27" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AY27" t="n">
         <v>16</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>12-1-2007-08</t>
+          <t>2007-12-01</t>
         </is>
       </c>
     </row>
@@ -5471,10 +5538,10 @@
         <v>-8.6</v>
       </c>
       <c r="AD28" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE28" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AF28" t="n">
         <v>30</v>
@@ -5483,10 +5550,10 @@
         <v>29</v>
       </c>
       <c r="AH28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ28" t="n">
         <v>2</v>
@@ -5501,7 +5568,7 @@
         <v>29</v>
       </c>
       <c r="AN28" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO28" t="n">
         <v>14</v>
@@ -5519,10 +5586,10 @@
         <v>8</v>
       </c>
       <c r="AT28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AU28" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AV28" t="n">
         <v>29</v>
@@ -5531,22 +5598,22 @@
         <v>10</v>
       </c>
       <c r="AX28" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY28" t="n">
         <v>18</v>
       </c>
       <c r="AZ28" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BA28" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BB28" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BC28" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>12-1-2007-08</t>
+          <t>2007-12-01</t>
         </is>
       </c>
     </row>
@@ -5575,16 +5642,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E29" t="n">
         <v>9</v>
       </c>
       <c r="F29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G29" t="n">
-        <v>0.529</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="H29" t="n">
         <v>48.3</v>
@@ -5593,40 +5660,40 @@
         <v>37.3</v>
       </c>
       <c r="J29" t="n">
-        <v>83.5</v>
+        <v>83.2</v>
       </c>
       <c r="K29" t="n">
-        <v>0.447</v>
+        <v>0.448</v>
       </c>
       <c r="L29" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="M29" t="n">
-        <v>20.3</v>
+        <v>19.9</v>
       </c>
       <c r="N29" t="n">
-        <v>0.426</v>
+        <v>0.428</v>
       </c>
       <c r="O29" t="n">
-        <v>15.5</v>
+        <v>15.8</v>
       </c>
       <c r="P29" t="n">
-        <v>18.4</v>
+        <v>18.8</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.843</v>
+        <v>0.841</v>
       </c>
       <c r="R29" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="S29" t="n">
-        <v>31.1</v>
+        <v>31.4</v>
       </c>
       <c r="T29" t="n">
-        <v>40.9</v>
+        <v>41.2</v>
       </c>
       <c r="U29" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="V29" t="n">
         <v>12.4</v>
@@ -5635,7 +5702,7 @@
         <v>6.8</v>
       </c>
       <c r="X29" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="Y29" t="n">
         <v>4.8</v>
@@ -5644,49 +5711,49 @@
         <v>21.1</v>
       </c>
       <c r="AA29" t="n">
-        <v>17.6</v>
+        <v>18.1</v>
       </c>
       <c r="AB29" t="n">
-        <v>98.7</v>
+        <v>98.8</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="AD29" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AE29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF29" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AG29" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AH29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ29" t="n">
         <v>7</v>
       </c>
       <c r="AK29" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AL29" t="n">
         <v>4</v>
       </c>
       <c r="AM29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AN29" t="n">
         <v>1</v>
       </c>
       <c r="AO29" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AP29" t="n">
         <v>30</v>
@@ -5698,13 +5765,13 @@
         <v>23</v>
       </c>
       <c r="AS29" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AT29" t="n">
         <v>23</v>
       </c>
       <c r="AU29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV29" t="n">
         <v>4</v>
@@ -5713,10 +5780,10 @@
         <v>23</v>
       </c>
       <c r="AX29" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AY29" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AZ29" t="n">
         <v>10</v>
@@ -5725,10 +5792,10 @@
         <v>30</v>
       </c>
       <c r="BB29" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BC29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>12-1-2007-08</t>
+          <t>2007-12-01</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5902,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD30" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE30" t="n">
         <v>4</v>
@@ -5847,7 +5914,7 @@
         <v>5</v>
       </c>
       <c r="AH30" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI30" t="n">
         <v>3</v>
@@ -5865,7 +5932,7 @@
         <v>30</v>
       </c>
       <c r="AN30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO30" t="n">
         <v>3</v>
@@ -5874,16 +5941,16 @@
         <v>3</v>
       </c>
       <c r="AQ30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR30" t="n">
         <v>10</v>
       </c>
       <c r="AS30" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU30" t="n">
         <v>1</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>12-1-2007-08</t>
+          <t>2007-12-01</t>
         </is>
       </c>
     </row>
@@ -5939,133 +6006,133 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F31" t="n">
         <v>9</v>
       </c>
       <c r="G31" t="n">
-        <v>0.471</v>
+        <v>0.438</v>
       </c>
       <c r="H31" t="n">
         <v>48.6</v>
       </c>
       <c r="I31" t="n">
-        <v>37.1</v>
+        <v>36.9</v>
       </c>
       <c r="J31" t="n">
-        <v>82.09999999999999</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>0.451</v>
+        <v>0.445</v>
       </c>
       <c r="L31" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="M31" t="n">
         <v>17.9</v>
       </c>
       <c r="N31" t="n">
-        <v>0.348</v>
+        <v>0.336</v>
       </c>
       <c r="O31" t="n">
-        <v>20.9</v>
+        <v>21.4</v>
       </c>
       <c r="P31" t="n">
-        <v>27</v>
+        <v>27.4</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.776</v>
+        <v>0.783</v>
       </c>
       <c r="R31" t="n">
-        <v>12.4</v>
+        <v>12.8</v>
       </c>
       <c r="S31" t="n">
-        <v>31.2</v>
+        <v>31.1</v>
       </c>
       <c r="T31" t="n">
-        <v>43.5</v>
+        <v>43.9</v>
       </c>
       <c r="U31" t="n">
-        <v>20.1</v>
+        <v>19.9</v>
       </c>
       <c r="V31" t="n">
         <v>15.1</v>
       </c>
       <c r="W31" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="X31" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Y31" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="Z31" t="n">
-        <v>21.1</v>
+        <v>21.7</v>
       </c>
       <c r="AA31" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="AB31" t="n">
         <v>101.3</v>
       </c>
       <c r="AC31" t="n">
-        <v>-0.4</v>
+        <v>-0.6</v>
       </c>
       <c r="AD31" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>9</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>16</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>14</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>20</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>9</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR31" t="n">
         <v>4</v>
       </c>
-      <c r="AE31" t="n">
-        <v>14</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG31" t="n">
+      <c r="AS31" t="n">
         <v>16</v>
       </c>
-      <c r="AH31" t="n">
-        <v>7</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>12</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>10</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>14</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>14</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>15</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>16</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>11</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR31" t="n">
+      <c r="AT31" t="n">
         <v>8</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>14</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>9</v>
       </c>
       <c r="AU31" t="n">
         <v>23</v>
@@ -6074,16 +6141,16 @@
         <v>12</v>
       </c>
       <c r="AW31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AX31" t="n">
         <v>6</v>
       </c>
       <c r="AY31" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AZ31" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="BA31" t="n">
         <v>13</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>12-1-2007-08</t>
+          <t>2007-12-01</t>
         </is>
       </c>
     </row>
